--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ASOCIACION CHILENA DE MUNICIPALIDADES</t>
+          <t>Asociación Chilena de Municipalidades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE SEGURIDAD PÚBLICA</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Servicio Nacional de la Discapacidad</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2159,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2285,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2350,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2415,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2480,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2545,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2610,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2736,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2801,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2866,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2931,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3057,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3183,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3248,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3313,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3378,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3508,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3573,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3638,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3703,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3685,7 +3833,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3746,7 +3898,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3807,7 +3963,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3868,7 +4028,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3929,7 +4093,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3990,7 +4158,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4051,7 +4223,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4112,7 +4288,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4173,7 +4353,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4234,7 +4418,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4295,7 +4483,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4356,7 +4548,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4417,7 +4613,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4478,7 +4678,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4600,7 +4804,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
